--- a/Beneficiarios_Indiretos.xlsx
+++ b/Beneficiarios_Indiretos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -429,42 +429,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Calton Mario</t>
+          <t>Aina Vasco</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calton Mario</t>
+          <t>Aina Vasco</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3918786000010338139</t>
+          <t>3918786000010526007</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Venda de produtos agricolas</t>
+          <t>Ajuda nas actividades de boa praticas Agrícolas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -474,34 +474,34 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>+258844009527</t>
+          <t>+258871048164</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carla Inocêncio </t>
+          <t>Filomena Abacar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carla Inocêncio</t>
+          <t>Filomena Abacar</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3918786000010338136</t>
+          <t>3918786000010526002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Venda de bolinhos</t>
+          <t>Venda de feijão fava</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>+258874560080</t>
+          <t>+258864152750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Victor Raja Leonel</t>
+          <t>Alima Elias</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Victor Raja Leonel</t>
+          <t>Alima Elias</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3918786000010299437</t>
+          <t>3918786000010525002</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Corte de arroz na machamba</t>
+          <t>Venda de farinha celeste</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -578,14 +578,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>+258876285264</t>
+          <t>+258869636778</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Romeu Botão </t>
+          <t>Calton Mario</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Manuel Romeu Botão</t>
+          <t>Calton Mario</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3918786000010299434</t>
+          <t>3918786000010338139</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Venda de galinha poedeira</t>
+          <t>Venda de produtos agricolas</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -625,39 +625,39 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>+258863542962</t>
+          <t>+258844009527</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosita Pilale</t>
+          <t xml:space="preserve">Carla Inocêncio </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rosita Pilale</t>
+          <t>Carla Inocêncio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3918786000010299429</t>
+          <t>3918786000010338136</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Procurar lenha</t>
+          <t>Venda de bolinhos</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -677,39 +677,39 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Começou ajudar no negócio da família</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>+258879658621</t>
+          <t>+258874560080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Vizinho</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Filomena Paiva</t>
+          <t>Victor Raja Leonel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Filomena Paiva</t>
+          <t>Victor Raja Leonel</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3918786000010299426</t>
+          <t>3918786000010299437</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -717,24 +717,24 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>+258863859632</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vender badjia</t>
+          <t>Corte de arroz na machamba</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou a trabalhar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>+258876285264</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Amaral </t>
+          <t xml:space="preserve">Manuel Romeu Botão </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sara Amaral</t>
+          <t>Manuel Romeu Botão</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3918786000010299421</t>
+          <t>3918786000010299434</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -769,51 +769,51 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>+258861532684</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Venda de mandioca fresca e cozida</t>
+          <t>Venda de galinha poedeira</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>+258863542962</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Vizinho</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ema Rui</t>
+          <t>Rosita Pilale</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ema Rui</t>
+          <t>Rosita Pilale</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3918786000010299418</t>
+          <t>3918786000010299429</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carregamento de milho na machamba </t>
+          <t>Procurar lenha</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -833,39 +833,39 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Começou a trabalhar no negócio da família</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>+258869524158</t>
+          <t>+258879658621</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marta Adelino</t>
+          <t>Filomena Paiva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Marta Adelino</t>
+          <t>Filomena Paiva</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3918786000010299413</t>
+          <t>3918786000010299426</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -873,9 +873,14 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>+258863859632</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venda de banana verde </t>
+          <t>Vender badjia</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -886,90 +891,85 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>Começou uma nova actividade geradora de renda</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>+258875236253</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Edson Mário</t>
+          <t xml:space="preserve">Sara Amaral </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Edson Mário</t>
+          <t>Sara Amaral</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3918786000010299410</t>
+          <t>3918786000010299421</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>+258861532684</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Debulha do milho</t>
+          <t>Venda de mandioca fresca e cozida</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Começou ajudar no negócio da família</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>+258842395652</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rito Sarito</t>
+          <t>Ema Rui</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rito Sarito</t>
+          <t>Ema Rui</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3918786000010299405</t>
+          <t>3918786000010299418</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -979,49 +979,49 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Venda de feijao cute</t>
+          <t xml:space="preserve">Carregamento de milho na machamba </t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou a trabalhar no negócio da família</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>+258868326323</t>
+          <t>+258869524158</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Faita Romeu</t>
+          <t>Marta Adelino</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Faita Romeu</t>
+          <t>Marta Adelino</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3918786000010299402</t>
+          <t>3918786000010299413</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ajuda a fazer os registos na banca</t>
+          <t xml:space="preserve">Venda de banana verde </t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1041,62 +1041,218 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Começou a trabalhar no negócio da família</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>+258860032523</t>
+          <t>+258875236253</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Vizinho</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Edson Mário</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Edson Mário</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3918786000010299410</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Debulha do milho</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Começou ajudar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>+258842395652</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Membro da Família</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rito Sarito</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rito Sarito</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3918786000010299405</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Venda de feijao cute</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>+258868326323</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Membro da comunidade</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Faita Romeu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Faita Romeu</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3918786000010299402</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ajuda a fazer os registos na banca</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Começou a trabalhar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>+258860032523</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Membro da Família</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Celia constantino</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Celia constantino</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>3918786000010286058</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>+258863199673</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Começou a vender bolinhos da mãe em sua ausência </t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Feminino</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Começou ajudar no negócio da família</t>
         </is>
@@ -1363,13 +1519,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE7EAE8-FE6C-4EF6-839C-D1E5D4294098}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C435ABF6-8F8B-432C-B87D-A465B9D10D97}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F66641-2CA7-4374-9621-2C61A63344C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18F3E3D0-74D6-4AF9-B583-827E2345B594}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02F681C4-2540-4FAD-9F19-A73CB1291F22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553813F4-364F-4482-8625-B138E47CA708}"/>
 </file>
--- a/Beneficiarios_Indiretos.xlsx
+++ b/Beneficiarios_Indiretos.xlsx
@@ -1519,13 +1519,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C435ABF6-8F8B-432C-B87D-A465B9D10D97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B9D8538-371B-471E-8E88-256500138BA7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18F3E3D0-74D6-4AF9-B583-827E2345B594}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECE78F7C-D429-491C-8238-C328925DA51E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553813F4-364F-4482-8625-B138E47CA708}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC8F0C7E-7CBF-429F-83C7-D6AFFEFDD276}"/>
 </file>
--- a/Beneficiarios_Indiretos.xlsx
+++ b/Beneficiarios_Indiretos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -434,47 +434,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aina Vasco</t>
+          <t>Capilai Carlito</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aina Vasco</t>
+          <t>Capilai Carlito</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3918786000010526007</t>
+          <t>3918786000011088016</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ajuda nas actividades de boa praticas Agrícolas</t>
+          <t xml:space="preserve">Dei-lhe conhecimentos que recebi do projeto até ao ponto de ele começar a fazer negócio </t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Começou ajudar no negócio da família</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>+258871048164</t>
+          <t>+258877181666</t>
         </is>
       </c>
     </row>
@@ -486,22 +486,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Filomena Abacar</t>
+          <t>Razaque Riquiso</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filomena Abacar</t>
+          <t>Razaque Riquiso</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3918786000010526002</t>
+          <t>3918786000011081147</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -511,12 +511,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Venda de feijão fava</t>
+          <t xml:space="preserve">Venda de badjias </t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>+258864152750</t>
+          <t>+258874972078</t>
         </is>
       </c>
     </row>
@@ -538,22 +538,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Alima Elias</t>
+          <t xml:space="preserve">Eurelio António </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alima Elias</t>
+          <t>Eurelio António</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3918786000010525002</t>
+          <t>3918786000011081142</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Venda de farinha celeste</t>
+          <t xml:space="preserve">Fica a vender os produtos almentares na ausência do irmão </t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -578,34 +578,34 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>+258869636778</t>
+          <t>+258869881240</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Calton Mario</t>
+          <t>Zinha Manuença</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calton Mario</t>
+          <t>Zinha Manuença</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3918786000010338139</t>
+          <t>3918786000010783016</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -615,49 +615,49 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Venda de produtos agricolas</t>
+          <t>Venda de comida (xima)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Começou ajudar no negócio da família</t>
+          <t>Começou a trabalhar no negócio da família</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>+258844009527</t>
+          <t>+258863199673</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carla Inocêncio </t>
+          <t>Laurinda Eduardo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carla Inocêncio</t>
+          <t>Laurinda Eduardo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3918786000010338136</t>
+          <t>3918786000010783011</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Venda de bolinhos</t>
+          <t>Começou a traduzir e vender badjias depois que o marido falou-lhe sobre Iniciativa Pessoal</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -682,34 +682,34 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>+258874560080</t>
+          <t>+258879445721</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Victor Raja Leonel</t>
+          <t>Adinane</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Victor Raja Leonel</t>
+          <t>Adinane</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3918786000010299437</t>
+          <t>3918786000010783008</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Corte de arroz na machamba</t>
+          <t>Contratado para ensacar e carregar  carvao</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -729,39 +729,39 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Começou a trabalhar no negócio da família</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>+258876285264</t>
+          <t>+258879445721</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Romeu Botão </t>
+          <t>Octavio Raimundo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Manuel Romeu Botão</t>
+          <t>Octavio Raimundo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3918786000010299434</t>
+          <t>3918786000010783005</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Venda de galinha poedeira</t>
+          <t>Contratado para queimar carvao</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -781,39 +781,39 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>+258863542962</t>
+          <t>+258879445721</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosita Pilale</t>
+          <t xml:space="preserve">Nelson Guilherme </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rosita Pilale</t>
+          <t>Nelson Guilherme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3918786000010299429</t>
+          <t>3918786000010783002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Procurar lenha</t>
+          <t>Contratado para queimar carvao</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -838,49 +838,44 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>+258879658621</t>
+          <t>+258867855454</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Filomena Paiva</t>
+          <t>Aina Vasco</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Filomena Paiva</t>
+          <t>Aina Vasco</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3918786000010299426</t>
+          <t>3918786000010526007</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>+258863859632</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vender badjia</t>
+          <t>Ajuda nas actividades de boa praticas Agrícolas</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -890,7 +885,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>+258871048164</t>
         </is>
       </c>
     </row>
@@ -902,22 +902,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Amaral </t>
+          <t>Filomena Abacar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sara Amaral</t>
+          <t>Filomena Abacar</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3918786000010299421</t>
+          <t>3918786000010526002</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -925,14 +925,9 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>+258861532684</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Venda de mandioca fresca e cozida</t>
+          <t>Venda de feijão fava</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -942,34 +937,39 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>+258864152750</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ema Rui</t>
+          <t>Alima Elias</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ema Rui</t>
+          <t>Alima Elias</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3918786000010299418</t>
+          <t>3918786000010525002</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carregamento de milho na machamba </t>
+          <t>Venda de farinha celeste</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -994,34 +994,34 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>+258869524158</t>
+          <t>+258869636778</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marta Adelino</t>
+          <t>Calton Mario</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Marta Adelino</t>
+          <t>Calton Mario</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3918786000010299413</t>
+          <t>3918786000010338139</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1031,81 +1031,81 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venda de banana verde </t>
+          <t>Venda de produtos agricolas</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou ajudar no negócio da família</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>+258875236253</t>
+          <t>+258844009527</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vizinho</t>
+          <t>Membro da comunidade</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Edson Mário</t>
+          <t xml:space="preserve">Carla Inocêncio </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Edson Mário</t>
+          <t>Carla Inocêncio</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3918786000010299410</t>
+          <t>3918786000010338136</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Debulha do milho</t>
+          <t>Venda de bolinhos</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Começou ajudar no negócio da família</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>+258842395652</t>
+          <t>+258874560080</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Membro da Família</t>
+          <t>Vizinho</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1115,17 +1115,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rito Sarito</t>
+          <t>Victor Raja Leonel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rito Sarito</t>
+          <t>Victor Raja Leonel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3918786000010299405</t>
+          <t>3918786000010299437</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Venda de feijao cute</t>
+          <t>Corte de arroz na machamba</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1145,39 +1145,39 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Começou uma nova actividade geradora de renda</t>
+          <t>Começou a trabalhar no negócio da família</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>+258868326323</t>
+          <t>+258876285264</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Membro da comunidade</t>
+          <t>Membro da Família</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Faita Romeu</t>
+          <t xml:space="preserve">Manuel Romeu Botão </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Faita Romeu</t>
+          <t>Manuel Romeu Botão</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3918786000010299402</t>
+          <t>3918786000010299434</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1187,72 +1187,488 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ajuda a fazer os registos na banca</t>
+          <t>Venda de galinha poedeira</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Começou a trabalhar no negócio da família</t>
+          <t>Começou uma nova actividade geradora de renda</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>+258860032523</t>
+          <t>+258863542962</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Vizinho</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosita Pilale</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rosita Pilale</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3918786000010299429</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Procurar lenha</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Começou ajudar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>+258879658621</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Membro da comunidade</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Filomena Paiva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Filomena Paiva</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3918786000010299426</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>+258863859632</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Vender badjia</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Membro da Família</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara Amaral </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sara Amaral</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3918786000010299421</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>+258861532684</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Venda de mandioca fresca e cozida</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Membro da comunidade</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ema Rui</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ema Rui</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3918786000010299418</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carregamento de milho na machamba </t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Começou a trabalhar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>+258869524158</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Membro da Família</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Marta Adelino</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Marta Adelino</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3918786000010299413</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venda de banana verde </t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>+258875236253</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vizinho</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Edson Mário</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Edson Mário</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3918786000010299410</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Debulha do milho</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Começou ajudar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>+258842395652</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Membro da Família</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rito Sarito</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rito Sarito</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3918786000010299405</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Venda de feijao cute</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Começou uma nova actividade geradora de renda</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>+258868326323</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Membro da comunidade</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Faita Romeu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Faita Romeu</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3918786000010299402</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ajuda a fazer os registos na banca</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Começou a trabalhar no negócio da família</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>+258860032523</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Membro da Família</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Celia constantino</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Celia constantino</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>3918786000010286058</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>+258863199673</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Começou a vender bolinhos da mãe em sua ausência </t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Feminino</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Começou ajudar no negócio da família</t>
         </is>
@@ -1519,13 +1935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B9D8538-371B-471E-8E88-256500138BA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA10519-5545-458A-BCAE-57E73702D908}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECE78F7C-D429-491C-8238-C328925DA51E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD604BD-CAA4-4A56-BBA4-C2C8D4EFE2A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC8F0C7E-7CBF-429F-83C7-D6AFFEFDD276}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B2FAA6C-7792-4C93-9E26-37A4F3F87EE0}"/>
 </file>
--- a/Beneficiarios_Indiretos.xlsx
+++ b/Beneficiarios_Indiretos.xlsx
@@ -1935,13 +1935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA10519-5545-458A-BCAE-57E73702D908}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0883DFFA-2476-45E3-A970-30AFE53977C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD604BD-CAA4-4A56-BBA4-C2C8D4EFE2A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9166B37D-4146-460C-90A8-78BFF0E0242D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B2FAA6C-7792-4C93-9E26-37A4F3F87EE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B68B952-610C-475E-8F43-81B58C921A0B}"/>
 </file>
--- a/Beneficiarios_Indiretos.xlsx
+++ b/Beneficiarios_Indiretos.xlsx
@@ -1935,13 +1935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0883DFFA-2476-45E3-A970-30AFE53977C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ED7D3D0-5EFD-4F12-896A-E6A2AB5B6B74}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9166B37D-4146-460C-90A8-78BFF0E0242D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F10A55AB-519B-4192-BE12-517203EC3BB5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B68B952-610C-475E-8F43-81B58C921A0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75CBD7B8-86E9-4CD2-BD45-184CE24E399C}"/>
 </file>